--- a/datasets/day1_excel_foundations/03_worksheets_and_navigation/d1_m3_worksheets_answers.xlsx
+++ b/datasets/day1_excel_foundations/03_worksheets_and_navigation/d1_m3_worksheets_answers.xlsx
@@ -527,7 +527,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>119.7</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
@@ -558,7 +558,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>56.1</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
@@ -589,7 +589,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>102.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -620,7 +620,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>258.4</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6">
@@ -651,7 +651,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>159</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
@@ -713,7 +713,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>3332</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="9">
@@ -744,7 +744,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1454.4</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="10">
@@ -775,7 +775,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>779.2</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11">
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>801.6</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="12">
@@ -837,7 +837,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1663</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="13">
@@ -868,7 +868,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1758</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="14">
@@ -899,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1148</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="15">
@@ -930,7 +930,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>905.25</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="16">
@@ -961,7 +961,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>882</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="17">
@@ -992,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1696</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="18">
@@ -1023,7 +1023,7 @@
         <v>4</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>4416</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="19">
@@ -1054,7 +1054,7 @@
         <v>3</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>326.25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20">
@@ -1085,7 +1085,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>177</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
@@ -1116,7 +1116,7 @@
         <v>2</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>619.4</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22">
@@ -1147,7 +1147,7 @@
         <v>2</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>370</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23">
@@ -1178,7 +1178,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>190.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
@@ -1209,7 +1209,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>263</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25">
@@ -1240,7 +1240,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>352</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26">
@@ -1271,7 +1271,7 @@
         <v>1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>148</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27">
@@ -1302,7 +1302,7 @@
         <v>2</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>226</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28">
@@ -1333,7 +1333,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>289.85</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29">
@@ -1364,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>115.9</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30">
@@ -1426,7 +1426,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>806</v>
+        <v>600</v>
       </c>
     </row>
     <row r="32">
@@ -1457,7 +1457,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1656</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="33">
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>724</v>
+        <v>800</v>
       </c>
     </row>
     <row r="34">
@@ -1519,7 +1519,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>653.8</v>
+        <v>800</v>
       </c>
     </row>
     <row r="35">
@@ -1550,7 +1550,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>918</v>
+        <v>600</v>
       </c>
     </row>
     <row r="36">
@@ -1581,7 +1581,7 @@
         <v>2</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1160</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="37">
@@ -1612,7 +1612,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>587.2</v>
+        <v>600</v>
       </c>
     </row>
     <row r="38">
@@ -1643,7 +1643,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>1037</v>
+        <v>600</v>
       </c>
     </row>
     <row r="39">
@@ -1674,7 +1674,7 @@
         <v>3</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1806.9</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="40">
@@ -1705,7 +1705,7 @@
         <v>1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>672.8</v>
+        <v>700</v>
       </c>
     </row>
     <row r="41">
@@ -1736,7 +1736,7 @@
         <v>1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>889.1</v>
+        <v>700</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3332</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="3">
@@ -1843,7 +1843,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1454.4</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="4">
@@ -1869,7 +1869,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>779.2</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5">
@@ -1895,7 +1895,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>801.6</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="6">
@@ -1921,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1663</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="7">
@@ -1947,7 +1947,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1758</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="8">
@@ -1973,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1148</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="9">
@@ -1999,7 +1999,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>905.25</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="10">
@@ -2025,7 +2025,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>882</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="11">
@@ -2051,7 +2051,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1696</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12">
@@ -2077,7 +2077,7 @@
         <v>4</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4416</v>
+        <v>6000</v>
       </c>
     </row>
   </sheetData>
@@ -2184,7 +2184,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>806</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4">
@@ -2210,7 +2210,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1656</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="5">
@@ -2236,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>724</v>
+        <v>800</v>
       </c>
     </row>
     <row r="6">
@@ -2262,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>653.8</v>
+        <v>800</v>
       </c>
     </row>
     <row r="7">
@@ -2288,7 +2288,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>918</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -2314,7 +2314,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1160</v>
+        <v>1200</v>
       </c>
     </row>
   </sheetData>
@@ -2395,7 +2395,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>587.2</v>
+        <v>600</v>
       </c>
     </row>
     <row r="3">
@@ -2421,7 +2421,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1037</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4">
@@ -2447,7 +2447,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1806.9</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5">
@@ -2473,7 +2473,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>672.8</v>
+        <v>700</v>
       </c>
     </row>
     <row r="6">
@@ -2499,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>889.1</v>
+        <v>700</v>
       </c>
     </row>
   </sheetData>
@@ -2580,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>119.7</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
@@ -2606,7 +2606,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>56.1</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
@@ -2632,7 +2632,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>102.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -2658,7 +2658,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>258.4</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6">
@@ -2684,7 +2684,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>159</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -2710,7 +2710,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2791,7 +2791,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>326.25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3">
@@ -2817,7 +2817,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>177</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -2843,7 +2843,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>619.4</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
@@ -2869,7 +2869,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>370</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6">
@@ -2895,7 +2895,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>190.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -2921,7 +2921,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>263</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
@@ -2947,7 +2947,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>352</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9">
@@ -2973,7 +2973,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>148</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -2999,7 +2999,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>226</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11">
@@ -3025,7 +3025,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>289.85</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12">
@@ -3051,7 +3051,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>115.9</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/day1_excel_foundations/03_worksheets_and_navigation/d1_m3_worksheets_answers.xlsx
+++ b/datasets/day1_excel_foundations/03_worksheets_and_navigation/d1_m3_worksheets_answers.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
@@ -533,20 +533,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O0017</t>
+          <t>O0009</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46011</v>
+        <v>46084</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tatenda Mpofu</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bluetooth Headphones</t>
+          <t>USB-C Hub 7in1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -555,29 +555,29 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O0028</t>
+          <t>O0015</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46162</v>
+        <v>46210</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Laptop Sleeve 15in</t>
+          <t>Wireless Mouse Pro</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -589,26 +589,26 @@
         <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O0029</t>
+          <t>O0018</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45498</v>
+        <v>45902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bluetooth Headphones</t>
+          <t>Laptop Sleeve 15in</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -617,51 +617,51 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>240</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O0031</t>
+          <t>O0003</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45855</v>
+        <v>45481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>USB-C Hub 7in1</t>
+          <t>Dell XPS 15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Accessory</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>80</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O0036</t>
+          <t>O0004</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45481</v>
+        <v>46249</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -670,38 +670,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wireless Mouse Pro</t>
+          <t>ThinkPad X1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Accessory</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>60</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O0003</t>
+          <t>O0008</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45481</v>
+        <v>45533</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tendai Moyo</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Dell XPS 15</t>
+          <t>MacBook Air M4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -710,29 +710,29 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O0004</t>
+          <t>O0013</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46249</v>
+        <v>46365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Tatenda Mpofu</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>HP Spectre x360</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -741,320 +741,320 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1400</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O0008</t>
+          <t>O0006</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45533</v>
+        <v>45694</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MacBook Air M4</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O0010</t>
+          <t>O0012</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45383</v>
+        <v>45944</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HP Spectre x360</t>
+          <t>Echo Dot 6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O0011</t>
+          <t>O0017</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46317</v>
+        <v>46347</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Google Nest Hub 3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1400</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O0016</t>
+          <t>O0020</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46107</v>
+        <v>45824</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1400</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O0018</t>
+          <t>O0001</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45508</v>
+        <v>46039</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>iPhone 16</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O0019</t>
+          <t>O0007</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45671</v>
+        <v>45922</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O0025</t>
+          <t>O0011</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46363</v>
+        <v>46200</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Pixel 9 Pro</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1400</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O0027</t>
+          <t>O0016</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46252</v>
+        <v>45734</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Simbarashe Mutasa</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MacBook Air M4</t>
+          <t>OnePlus 13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O0037</t>
+          <t>O0005</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46001</v>
+        <v>46123</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Simbarashe Mutasa</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Dell XPS 15</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>6000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O0007</t>
+          <t>O0010</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45458</v>
+        <v>45796</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Surface Go 4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smart Home</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>3</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>300</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="20">
@@ -1064,679 +1064,59 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45453</v>
+        <v>45682</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy Tab S10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smart Home</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O0023</t>
+          <t>O0019</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45522</v>
+        <v>46065</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Google Nest Hub 3</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Smart Home</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>2</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>O0024</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Farai Ncube</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>O0026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>46017</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Tendai Moyo</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Echo Dot 6</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>O0030</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>46183</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Simbarashe Mutasa</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Ring Doorbell Pro</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>O0032</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Rutendo Chikafu</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>O0033</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>46040</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Tendai Moyo</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Ring Doorbell Pro</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>O0034</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>45832</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Amara Otieno</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>O0035</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Kagiso Molefe</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>O0040</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>46243</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Farai Ncube</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Ring Doorbell Pro</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>O0001</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>46039</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Amara Otieno</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>iPhone 16</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>O0005</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>46123</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Chipo Marufu</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>OnePlus 13</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>O0006</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>45938</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Amara Otieno</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Galaxy S24</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>O0013</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>45994</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Chipo Marufu</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Galaxy S24</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>O0015</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>46287</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Galaxy S24</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>O0020</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>45306</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Rutendo Chikafu</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>OnePlus 13</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>O0038</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>45940</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Amara Otieno</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>OnePlus 13</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>2</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>O0009</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>45856</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Chipo Marufu</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Surface Go 4</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>O0012</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>45857</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Tendai Moyo</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Surface Go 4</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>O0021</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>45939</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Kudzai Sibanda</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Galaxy Tab S10</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>O0022</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>45884</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>iPad Air 6</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>O0039</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Rutendo Chikafu</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>iPad Air 6</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>700</v>
+        <v>1400</v>
       </c>
     </row>
   </sheetData>
@@ -1751,12 +1131,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="19.5" customWidth="1" min="3" max="3"/>
+    <col width="16.5" customWidth="1" min="3" max="3"/>
     <col width="17.5" customWidth="1" min="4" max="4"/>
     <col width="10.5" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
@@ -1814,10 +1194,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="3">
@@ -1840,10 +1220,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1400</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="4">
@@ -1875,15 +1255,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O0010</t>
+          <t>O0013</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45383</v>
+        <v>46365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Tatenda Mpofu</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1892,192 +1272,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>O0011</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>46317</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Kudzai Sibanda</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ThinkPad X1</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>O0016</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>46107</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ThinkPad X1</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>O0018</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45508</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Chipo Marufu</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ThinkPad X1</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>O0019</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45671</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Kudzai Sibanda</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ThinkPad X1</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>O0025</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>46363</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ThinkPad X1</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>O0027</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Simbarashe Mutasa</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>MacBook Air M4</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>O0037</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>46001</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Simbarashe Mutasa</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Dell XPS 15</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>6000</v>
+        <v>2400</v>
       </c>
     </row>
   </sheetData>
@@ -2092,13 +1290,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
     <col width="17.5" customWidth="1" min="3" max="3"/>
-    <col width="12.5" customWidth="1" min="4" max="4"/>
+    <col width="13.5" customWidth="1" min="4" max="4"/>
     <col width="10.5" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2164,157 +1362,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O0005</t>
+          <t>O0007</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46123</v>
+        <v>45922</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O0006</t>
+          <t>O0011</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45938</v>
+        <v>46200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amara Otieno</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Pixel 9 Pro</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>2</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O0013</t>
+          <t>O0016</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45994</v>
+        <v>45734</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>OnePlus 13</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>O0015</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>46287</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Galaxy S24</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>O0020</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45306</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Rutendo Chikafu</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>OnePlus 13</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3" t="n">
         <v>600</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>O0038</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45940</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Amara Otieno</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>OnePlus 13</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>1200</v>
       </c>
     </row>
   </sheetData>
@@ -2329,12 +1449,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="17.5" customWidth="1" min="3" max="3"/>
+    <col width="14.5" customWidth="1" min="3" max="3"/>
     <col width="16.5" customWidth="1" min="4" max="4"/>
     <col width="10.5" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
@@ -2375,11 +1495,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>O0009</t>
+          <t>O0005</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45856</v>
+        <v>46123</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2388,28 +1508,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O0012</t>
+          <t>O0010</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45857</v>
+        <v>45796</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tendai Moyo</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2418,24 +1538,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O0021</t>
+          <t>O0014</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45939</v>
+        <v>45682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2444,24 +1564,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O0022</t>
+          <t>O0019</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45884</v>
+        <v>46065</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2470,36 +1590,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>O0039</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Rutendo Chikafu</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>iPad Air 6</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>700</v>
+        <v>1400</v>
       </c>
     </row>
   </sheetData>
@@ -2514,12 +1608,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="16.5" customWidth="1" min="3" max="3"/>
+    <col width="17.5" customWidth="1" min="3" max="3"/>
     <col width="22.5" customWidth="1" min="4" max="4"/>
     <col width="10.5" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
@@ -2586,131 +1680,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O0017</t>
+          <t>O0009</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46011</v>
+        <v>46084</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tatenda Mpofu</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bluetooth Headphones</t>
+          <t>USB-C Hub 7in1</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O0028</t>
+          <t>O0015</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46162</v>
+        <v>46210</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Laptop Sleeve 15in</t>
+          <t>Wireless Mouse Pro</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O0029</t>
+          <t>O0018</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45498</v>
+        <v>45902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bluetooth Headphones</t>
+          <t>Laptop Sleeve 15in</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>O0031</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45855</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Nyasha Banda</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>USB-C Hub 7in1</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>O0036</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45481</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Kudzai Sibanda</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Wireless Mouse Pro</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2725,7 +1767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
@@ -2771,41 +1813,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>O0007</t>
+          <t>O0006</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45458</v>
+        <v>45694</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O0014</t>
+          <t>O0012</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45453</v>
+        <v>45944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2823,11 +1865,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O0023</t>
+          <t>O0017</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45522</v>
+        <v>46347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2840,20 +1882,20 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O0024</t>
+          <t>O0020</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46343</v>
+        <v>45824</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2862,195 +1904,13 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Google Nest Hub 3</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>O0026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>46017</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Tendai Moyo</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Echo Dot 6</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>O0030</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>46183</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Simbarashe Mutasa</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ring Doorbell Pro</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>O0032</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Rutendo Chikafu</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>O0033</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>46040</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Tendai Moyo</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Ring Doorbell Pro</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>O0034</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45832</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Amara Otieno</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>O0035</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Kagiso Molefe</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>O0040</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>46243</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Farai Ncube</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Ring Doorbell Pro</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="3" t="n">
         <v>200</v>
       </c>
     </row>
